--- a/Team-Data/2008-09/1-30-2008-09.xlsx
+++ b/Team-Data/2008-09/1-30-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
         <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>0.587</v>
+        <v>0.578</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -679,10 +746,10 @@
         <v>36</v>
       </c>
       <c r="J2" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L2" t="n">
         <v>7.8</v>
@@ -691,16 +758,16 @@
         <v>21.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O2" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="P2" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.74</v>
+        <v>0.737</v>
       </c>
       <c r="R2" t="n">
         <v>10.5</v>
@@ -709,7 +776,7 @@
         <v>29.7</v>
       </c>
       <c r="T2" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U2" t="n">
         <v>21.3</v>
@@ -718,7 +785,7 @@
         <v>13.1</v>
       </c>
       <c r="W2" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X2" t="n">
         <v>4.7</v>
@@ -727,19 +794,19 @@
         <v>4.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>10</v>
@@ -751,37 +818,37 @@
         <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
         <v>19</v>
@@ -793,7 +860,7 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
         <v>12</v>
@@ -805,13 +872,13 @@
         <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -861,7 +928,7 @@
         <v>37.2</v>
       </c>
       <c r="J3" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
         <v>0.483</v>
@@ -870,73 +937,73 @@
         <v>6.7</v>
       </c>
       <c r="M3" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.39</v>
       </c>
       <c r="O3" t="n">
         <v>20.4</v>
       </c>
       <c r="P3" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.8</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.4</v>
+        <v>101.5</v>
       </c>
       <c r="AC3" t="n">
         <v>10.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -945,13 +1012,13 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM3" t="n">
         <v>17</v>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
         <v>7</v>
@@ -960,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
@@ -969,7 +1036,7 @@
         <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
@@ -981,19 +1048,19 @@
         <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -1025,19 +1092,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
         <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>0.404</v>
+        <v>0.413</v>
       </c>
       <c r="H4" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I4" t="n">
         <v>34</v>
@@ -1046,16 +1113,16 @@
         <v>76.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M4" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.358</v>
+        <v>0.355</v>
       </c>
       <c r="O4" t="n">
         <v>18.4</v>
@@ -1070,16 +1137,16 @@
         <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="T4" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V4" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
@@ -1094,25 +1161,25 @@
         <v>22.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>92</v>
+        <v>91.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
         <v>1</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1133,7 +1200,7 @@
         <v>25</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
         <v>21</v>
@@ -1142,13 +1209,13 @@
         <v>17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR4" t="n">
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
         <v>26</v>
@@ -1163,7 +1230,7 @@
         <v>17</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1172,7 +1239,7 @@
         <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -1222,13 +1289,13 @@
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J5" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
@@ -1237,34 +1304,34 @@
         <v>16.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O5" t="n">
-        <v>18.3</v>
+        <v>18.7</v>
       </c>
       <c r="P5" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.788</v>
+        <v>0.792</v>
       </c>
       <c r="R5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
         <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U5" t="n">
         <v>21</v>
       </c>
       <c r="V5" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X5" t="n">
         <v>5.8</v>
@@ -1273,19 +1340,19 @@
         <v>5.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
         <v>99.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>20</v>
@@ -1297,7 +1364,7 @@
         <v>20</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1306,7 +1373,7 @@
         <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
         <v>20</v>
@@ -1315,13 +1382,13 @@
         <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AP5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1339,7 +1406,7 @@
         <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
         <v>13</v>
@@ -1351,10 +1418,10 @@
         <v>23</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -1392,82 +1459,82 @@
         <v>44</v>
       </c>
       <c r="E6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.795</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="J6" t="n">
-        <v>78.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="M6" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.379</v>
+        <v>0.372</v>
       </c>
       <c r="O6" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.754</v>
+        <v>0.751</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S6" t="n">
         <v>31.1</v>
       </c>
       <c r="T6" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="V6" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="W6" t="n">
         <v>7.8</v>
       </c>
       <c r="X6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.6</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.5</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.6</v>
+        <v>10.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1476,52 +1543,52 @@
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
         <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
@@ -1530,16 +1597,16 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
         <v>6</v>
@@ -1676,10 +1743,10 @@
         <v>13</v>
       </c>
       <c r="AM7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
         <v>25</v>
@@ -1706,10 +1773,10 @@
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY7" t="n">
         <v>9</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>0.66</v>
+        <v>0.652</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
@@ -1771,22 +1838,22 @@
         <v>36.9</v>
       </c>
       <c r="J8" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.472</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="n">
         <v>6.7</v>
       </c>
       <c r="M8" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O8" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="P8" t="n">
         <v>31.2</v>
@@ -1798,49 +1865,49 @@
         <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T8" t="n">
         <v>41.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V8" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="W8" t="n">
         <v>9.1</v>
       </c>
       <c r="X8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y8" t="n">
         <v>5.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AA8" t="n">
         <v>23.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.1</v>
+        <v>104</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
         <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
         <v>23</v>
@@ -1849,16 +1916,16 @@
         <v>12</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN8" t="n">
         <v>14</v>
@@ -1894,13 +1961,13 @@
         <v>3</v>
       </c>
       <c r="AY8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -1935,37 +2002,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" t="n">
-        <v>0.556</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="J9" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L9" t="n">
         <v>4.6</v>
       </c>
       <c r="M9" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.338</v>
+        <v>0.341</v>
       </c>
       <c r="O9" t="n">
         <v>17</v>
@@ -1980,79 +2047,79 @@
         <v>10.6</v>
       </c>
       <c r="S9" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T9" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U9" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V9" t="n">
         <v>12</v>
       </c>
       <c r="W9" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA9" t="n">
         <v>20.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
         <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM9" t="n">
         <v>27</v>
       </c>
-      <c r="AM9" t="n">
-        <v>28</v>
-      </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
         <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR9" t="n">
         <v>18</v>
@@ -2064,7 +2131,7 @@
         <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2073,7 +2140,7 @@
         <v>26</v>
       </c>
       <c r="AX9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
         <v>4</v>
@@ -2082,13 +2149,13 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
         <v>27</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
         <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>0.319</v>
+        <v>0.304</v>
       </c>
       <c r="H10" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I10" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J10" t="n">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="K10" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L10" t="n">
         <v>6.5</v>
@@ -2147,28 +2214,28 @@
         <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O10" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="P10" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R10" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S10" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T10" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U10" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
@@ -2177,25 +2244,25 @@
         <v>7.9</v>
       </c>
       <c r="X10" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y10" t="n">
         <v>5.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>106.7</v>
+        <v>107</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.6</v>
+        <v>-4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>25</v>
@@ -2225,7 +2292,7 @@
         <v>16</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -2234,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
         <v>5</v>
@@ -2246,13 +2313,13 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
@@ -2264,7 +2331,7 @@
         <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2389,10 +2456,10 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ11" t="n">
         <v>17</v>
@@ -2401,7 +2468,7 @@
         <v>25</v>
       </c>
       <c r="AL11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM11" t="n">
         <v>9</v>
@@ -2419,7 +2486,7 @@
         <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
         <v>3</v>
@@ -2428,7 +2495,7 @@
         <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV11" t="n">
         <v>13</v>
@@ -2440,7 +2507,7 @@
         <v>29</v>
       </c>
       <c r="AY11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -2481,19 +2548,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
         <v>28</v>
       </c>
       <c r="G12" t="n">
-        <v>0.404</v>
+        <v>0.391</v>
       </c>
       <c r="H12" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I12" t="n">
         <v>39</v>
@@ -2502,25 +2569,25 @@
         <v>86.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L12" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M12" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.367</v>
+        <v>0.363</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P12" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.806</v>
+        <v>0.804</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
@@ -2529,7 +2596,7 @@
         <v>32.3</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U12" t="n">
         <v>22.8</v>
@@ -2547,31 +2614,31 @@
         <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.5</v>
+        <v>104.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.1</v>
+        <v>-2.4</v>
       </c>
       <c r="AD12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH12" t="n">
         <v>4</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>5</v>
       </c>
       <c r="AI12" t="n">
         <v>2</v>
@@ -2583,19 +2650,19 @@
         <v>16</v>
       </c>
       <c r="AL12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM12" t="n">
         <v>8</v>
       </c>
-      <c r="AM12" t="n">
-        <v>7</v>
-      </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
         <v>17</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ12" t="n">
         <v>6</v>
@@ -2616,16 +2683,16 @@
         <v>23</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY12" t="n">
         <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
         <v>12</v>
@@ -2634,7 +2701,7 @@
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>0.217</v>
+        <v>0.222</v>
       </c>
       <c r="H13" t="n">
         <v>48.7</v>
@@ -2681,43 +2748,43 @@
         <v>35.1</v>
       </c>
       <c r="J13" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K13" t="n">
-        <v>0.427</v>
+        <v>0.428</v>
       </c>
       <c r="L13" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>0.328</v>
       </c>
       <c r="O13" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P13" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.751</v>
+        <v>0.749</v>
       </c>
       <c r="R13" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S13" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T13" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U13" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V13" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
@@ -2729,19 +2796,19 @@
         <v>5.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB13" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8</v>
+        <v>-7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,10 +2820,10 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2765,13 +2832,13 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO13" t="n">
         <v>26</v>
@@ -2783,22 +2850,22 @@
         <v>24</v>
       </c>
       <c r="AR13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS13" t="n">
         <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AV13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2807,10 +2874,10 @@
         <v>28</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -2860,79 +2927,79 @@
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>40.1</v>
+        <v>39.9</v>
       </c>
       <c r="J14" t="n">
-        <v>84.2</v>
+        <v>83.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L14" t="n">
         <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.376</v>
+        <v>0.38</v>
       </c>
       <c r="O14" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="P14" t="n">
-        <v>27.5</v>
+        <v>27.1</v>
       </c>
       <c r="Q14" t="n">
         <v>0.769</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
         <v>13.8</v>
       </c>
       <c r="W14" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X14" t="n">
         <v>5.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.5</v>
+        <v>107.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
         <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3</v>
       </c>
       <c r="AH14" t="n">
         <v>21</v>
@@ -2944,7 +3011,7 @@
         <v>4</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2962,13 +3029,13 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2986,13 +3053,13 @@
         <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,7 +3184,7 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
         <v>29</v>
@@ -3126,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="n">
         <v>28</v>
@@ -3135,7 +3202,7 @@
         <v>26</v>
       </c>
       <c r="AN15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO15" t="n">
         <v>11</v>
@@ -3144,7 +3211,7 @@
         <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>25</v>
@@ -3159,7 +3226,7 @@
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
         <v>9</v>
@@ -3168,7 +3235,7 @@
         <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ15" t="n">
         <v>21</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" t="n">
         <v>25</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.556</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J16" t="n">
         <v>81</v>
       </c>
       <c r="K16" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="N16" t="n">
         <v>0.355</v>
       </c>
       <c r="O16" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="R16" t="n">
         <v>10.4</v>
@@ -3266,55 +3333,55 @@
         <v>12.6</v>
       </c>
       <c r="W16" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA16" t="n">
         <v>19.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>96.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
         <v>14</v>
       </c>
       <c r="AI16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
       </c>
       <c r="AM16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN16" t="n">
         <v>20</v>
@@ -3326,7 +3393,7 @@
         <v>23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR16" t="n">
         <v>23</v>
@@ -3350,19 +3417,19 @@
         <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC16" t="n">
         <v>14</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>15</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -3394,19 +3461,19 @@
         <v>49</v>
       </c>
       <c r="E17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>0.469</v>
+        <v>0.449</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J17" t="n">
         <v>81.5</v>
@@ -3415,13 +3482,13 @@
         <v>0.447</v>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O17" t="n">
         <v>19.7</v>
@@ -3430,25 +3497,25 @@
         <v>25.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.784</v>
+        <v>0.781</v>
       </c>
       <c r="R17" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
-        <v>41.7</v>
+        <v>41.5</v>
       </c>
       <c r="U17" t="n">
         <v>21.2</v>
       </c>
       <c r="V17" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W17" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X17" t="n">
         <v>3.7</v>
@@ -3457,16 +3524,16 @@
         <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,7 +3542,7 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3493,7 +3560,7 @@
         <v>19</v>
       </c>
       <c r="AL17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM17" t="n">
         <v>23</v>
@@ -3511,10 +3578,10 @@
         <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT17" t="n">
         <v>14</v>
@@ -3532,10 +3599,10 @@
         <v>28</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
         <v>6</v>
@@ -3544,7 +3611,7 @@
         <v>18</v>
       </c>
       <c r="BC17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -3573,52 +3640,52 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" t="n">
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G18" t="n">
-        <v>0.356</v>
+        <v>0.364</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J18" t="n">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L18" t="n">
         <v>5.7</v>
       </c>
       <c r="M18" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="O18" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="P18" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.767</v>
+        <v>0.763</v>
       </c>
       <c r="R18" t="n">
         <v>12.5</v>
       </c>
       <c r="S18" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T18" t="n">
         <v>42.3</v>
@@ -3627,37 +3694,37 @@
         <v>20.4</v>
       </c>
       <c r="V18" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="W18" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.7</v>
+        <v>98.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.4</v>
+        <v>-3.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
         <v>24</v>
@@ -3672,25 +3739,25 @@
         <v>6</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
         <v>21</v>
       </c>
       <c r="AM18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AP18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
         <v>3</v>
@@ -3711,7 +3778,7 @@
         <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY18" t="n">
         <v>30</v>
@@ -3720,10 +3787,10 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC18" t="n">
         <v>24</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" t="n">
         <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.426</v>
+        <v>0.435</v>
       </c>
       <c r="H19" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I19" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J19" t="n">
-        <v>80.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L19" t="n">
         <v>7.8</v>
@@ -3785,82 +3852,82 @@
         <v>20.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O19" t="n">
         <v>19.6</v>
       </c>
       <c r="P19" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.775</v>
+        <v>0.777</v>
       </c>
       <c r="R19" t="n">
         <v>11.1</v>
       </c>
       <c r="S19" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T19" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U19" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="V19" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W19" t="n">
         <v>7</v>
       </c>
       <c r="X19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y19" t="n">
         <v>5.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.09999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3.3</v>
+        <v>-3</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG19" t="n">
         <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ19" t="n">
         <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN19" t="n">
         <v>9</v>
@@ -3878,7 +3945,7 @@
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
         <v>20</v>
@@ -3896,16 +3963,16 @@
         <v>21</v>
       </c>
       <c r="AY19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA19" t="n">
         <v>18</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>27</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>17</v>
-      </c>
       <c r="BB19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -3937,82 +4004,82 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E20" t="n">
         <v>28</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>0.651</v>
+        <v>0.667</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>34.9</v>
+        <v>35.1</v>
       </c>
       <c r="J20" t="n">
         <v>76.3</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.46</v>
       </c>
       <c r="L20" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M20" t="n">
         <v>19.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.39</v>
+        <v>0.394</v>
       </c>
       <c r="O20" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P20" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="S20" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T20" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="U20" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="V20" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W20" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y20" t="n">
         <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD20" t="n">
         <v>30</v>
@@ -4021,37 +4088,37 @@
         <v>7</v>
       </c>
       <c r="AF20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG20" t="n">
         <v>6</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>7</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ20" t="n">
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
@@ -4066,7 +4133,7 @@
         <v>29</v>
       </c>
       <c r="AU20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
@@ -4075,13 +4142,13 @@
         <v>10</v>
       </c>
       <c r="AX20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
         <v>14</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
         <v>18</v>
@@ -4209,7 +4276,7 @@
         <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
@@ -4227,13 +4294,13 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ21" t="n">
         <v>7</v>
@@ -4251,7 +4318,7 @@
         <v>9</v>
       </c>
       <c r="AV21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW21" t="n">
         <v>14</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ21" t="n">
         <v>5</v>
@@ -4272,7 +4339,7 @@
         <v>6</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E22" t="n">
         <v>11</v>
       </c>
       <c r="F22" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G22" t="n">
-        <v>0.234</v>
+        <v>0.239</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J22" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L22" t="n">
         <v>4.1</v>
@@ -4331,7 +4398,7 @@
         <v>10.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.378</v>
+        <v>0.383</v>
       </c>
       <c r="O22" t="n">
         <v>19.6</v>
@@ -4340,10 +4407,10 @@
         <v>25.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R22" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S22" t="n">
         <v>31.1</v>
@@ -4352,16 +4419,16 @@
         <v>42.9</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="W22" t="n">
         <v>6.9</v>
       </c>
       <c r="X22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y22" t="n">
         <v>5.3</v>
@@ -4370,16 +4437,16 @@
         <v>20.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>96.3</v>
+        <v>96.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.3</v>
+        <v>-6</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4397,7 +4464,7 @@
         <v>16</v>
       </c>
       <c r="AJ22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK22" t="n">
         <v>18</v>
@@ -4409,28 +4476,28 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="n">
         <v>9</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
         <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT22" t="n">
         <v>5</v>
       </c>
       <c r="AU22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4445,13 +4512,13 @@
         <v>22</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
         <v>4</v>
@@ -4573,13 +4640,13 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI23" t="n">
         <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
         <v>9</v>
@@ -4621,13 +4688,13 @@
         <v>15</v>
       </c>
       <c r="AX23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>8</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>6</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -4665,85 +4732,85 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F24" t="n">
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J24" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="N24" t="n">
-        <v>0.329</v>
+        <v>0.326</v>
       </c>
       <c r="O24" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P24" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.74</v>
+        <v>0.744</v>
       </c>
       <c r="R24" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S24" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T24" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="U24" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V24" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W24" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X24" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z24" t="n">
         <v>20.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>96.7</v>
+        <v>96.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE24" t="n">
         <v>16</v>
@@ -4755,16 +4822,16 @@
         <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
         <v>11</v>
       </c>
       <c r="AJ24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4773,7 +4840,7 @@
         <v>29</v>
       </c>
       <c r="AN24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO24" t="n">
         <v>23</v>
@@ -4782,7 +4849,7 @@
         <v>18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR24" t="n">
         <v>2</v>
@@ -4791,25 +4858,25 @@
         <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY24" t="n">
         <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA24" t="n">
         <v>20</v>
@@ -4818,7 +4885,7 @@
         <v>22</v>
       </c>
       <c r="BC24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>0.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF25" t="n">
         <v>9</v>
@@ -4958,7 +5025,7 @@
         <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP25" t="n">
         <v>5</v>
@@ -4970,13 +5037,13 @@
         <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
@@ -4988,10 +5055,10 @@
         <v>13</v>
       </c>
       <c r="AY25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -5029,52 +5096,52 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.636</v>
+        <v>0.622</v>
       </c>
       <c r="H26" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J26" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O26" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="P26" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
         <v>13.2</v>
       </c>
       <c r="S26" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="T26" t="n">
         <v>40.9</v>
@@ -5083,7 +5150,7 @@
         <v>20.2</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
         <v>7</v>
@@ -5092,28 +5159,28 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.7</v>
+        <v>98.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG26" t="n">
         <v>8</v>
@@ -5122,13 +5189,13 @@
         <v>11</v>
       </c>
       <c r="AI26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>21</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>22</v>
-      </c>
       <c r="AK26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5137,13 +5204,13 @@
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP26" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
         <v>18</v>
@@ -5167,19 +5234,19 @@
         <v>18</v>
       </c>
       <c r="AX26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA26" t="n">
         <v>11</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -5211,61 +5278,61 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G27" t="n">
-        <v>0.208</v>
+        <v>0.213</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J27" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K27" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L27" t="n">
         <v>6.4</v>
       </c>
       <c r="M27" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O27" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="P27" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R27" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S27" t="n">
         <v>28.6</v>
       </c>
       <c r="T27" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="U27" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="V27" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="W27" t="n">
         <v>6.6</v>
@@ -5274,19 +5341,19 @@
         <v>3.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z27" t="n">
         <v>23.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.1</v>
       </c>
       <c r="AD27" t="n">
         <v>2</v>
@@ -5304,28 +5371,28 @@
         <v>8</v>
       </c>
       <c r="AI27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK27" t="n">
         <v>22</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>24</v>
       </c>
       <c r="AL27" t="n">
         <v>18</v>
       </c>
       <c r="AM27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN27" t="n">
         <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
         <v>4</v>
@@ -5334,16 +5401,16 @@
         <v>24</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV27" t="n">
         <v>25</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>26</v>
       </c>
       <c r="AW27" t="n">
         <v>25</v>
@@ -5352,7 +5419,7 @@
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5510,13 +5577,13 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>22</v>
@@ -5531,7 +5598,7 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -5575,46 +5642,46 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E29" t="n">
         <v>19</v>
       </c>
       <c r="F29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G29" t="n">
-        <v>0.396</v>
+        <v>0.404</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J29" t="n">
         <v>78.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L29" t="n">
         <v>6.3</v>
       </c>
       <c r="M29" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.382</v>
+        <v>0.384</v>
       </c>
       <c r="O29" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P29" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.823</v>
+        <v>0.822</v>
       </c>
       <c r="R29" t="n">
         <v>8.9</v>
@@ -5623,10 +5690,10 @@
         <v>30</v>
       </c>
       <c r="T29" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="U29" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V29" t="n">
         <v>13.5</v>
@@ -5641,16 +5708,16 @@
         <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA29" t="n">
         <v>20.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.1</v>
+        <v>-1.9</v>
       </c>
       <c r="AD29" t="n">
         <v>2</v>
@@ -5659,22 +5726,22 @@
         <v>20</v>
       </c>
       <c r="AF29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL29" t="n">
         <v>19</v>
@@ -5686,7 +5753,7 @@
         <v>6</v>
       </c>
       <c r="AO29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP29" t="n">
         <v>22</v>
@@ -5701,10 +5768,10 @@
         <v>16</v>
       </c>
       <c r="AT29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5716,13 +5783,13 @@
         <v>17</v>
       </c>
       <c r="AY29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -5757,64 +5824,64 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
         <v>21</v>
       </c>
       <c r="G30" t="n">
-        <v>0.553</v>
+        <v>0.543</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="J30" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L30" t="n">
         <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.339</v>
+        <v>0.337</v>
       </c>
       <c r="O30" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="P30" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="R30" t="n">
         <v>12.1</v>
       </c>
       <c r="S30" t="n">
-        <v>29.2</v>
+        <v>29.4</v>
       </c>
       <c r="T30" t="n">
-        <v>41.3</v>
+        <v>41.5</v>
       </c>
       <c r="U30" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="V30" t="n">
         <v>15</v>
       </c>
       <c r="W30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X30" t="n">
         <v>4.9</v>
@@ -5826,19 +5893,19 @@
         <v>22.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>101.9</v>
+        <v>101.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF30" t="n">
         <v>15</v>
@@ -5853,19 +5920,19 @@
         <v>5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK30" t="n">
         <v>5</v>
       </c>
       <c r="AL30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN30" t="n">
         <v>26</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>27</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>25</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,13 +5941,13 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
         <v>15</v>
@@ -5889,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
@@ -5901,7 +5968,7 @@
         <v>16</v>
       </c>
       <c r="AZ30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" t="n">
         <v>9</v>
       </c>
       <c r="F31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G31" t="n">
-        <v>0.196</v>
+        <v>0.2</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5963,22 +6030,22 @@
         <v>0.444</v>
       </c>
       <c r="L31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M31" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.319</v>
+        <v>0.322</v>
       </c>
       <c r="O31" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P31" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R31" t="n">
         <v>11.6</v>
@@ -5990,10 +6057,10 @@
         <v>39.6</v>
       </c>
       <c r="U31" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V31" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W31" t="n">
         <v>7.5</v>
@@ -6002,10 +6069,10 @@
         <v>4.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA31" t="n">
         <v>19.2</v>
@@ -6014,10 +6081,10 @@
         <v>93.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.5</v>
+        <v>-7.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
@@ -6029,13 +6096,13 @@
         <v>30</v>
       </c>
       <c r="AH31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK31" t="n">
         <v>26</v>
@@ -6068,7 +6135,7 @@
         <v>25</v>
       </c>
       <c r="AU31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
@@ -6077,10 +6144,10 @@
         <v>11</v>
       </c>
       <c r="AX31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-30-2008-09</t>
+          <t>2009-01-30</t>
         </is>
       </c>
     </row>
